--- a/stats for com eng/excel files/Ch07-02.xlsx
+++ b/stats for com eng/excel files/Ch07-02.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pin/Desktop/joint-repository/stats for com eng/excel files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5D827F-0F99-8741-9BD3-B3EC9E6943CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3EE7EE-A22B-CC41-A6EC-10A83500258A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="20480" windowHeight="11000" activeTab="2" xr2:uid="{03B4F964-AA62-42B4-B9BD-0893A8980E7C}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="96">
   <si>
     <t>Treatment Combination</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>effect</t>
+  </si>
+  <si>
+    <t>df</t>
   </si>
 </sst>
 </file>
@@ -748,6 +751,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -766,31 +773,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -800,7 +782,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
@@ -881,8 +884,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6400801" y="114300"/>
-          <a:ext cx="1818200" cy="1285875"/>
+          <a:off x="8456971" y="114300"/>
+          <a:ext cx="1960360" cy="1306184"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1549,31 +1552,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="51" t="s">
+      <c r="B1" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="52"/>
-      <c r="L1" s="51" t="s">
+      <c r="K1" s="55"/>
+      <c r="L1" s="54" t="s">
         <v>19</v>
       </c>
       <c r="M1" s="15"/>
       <c r="N1" s="15"/>
     </row>
     <row r="2" spans="1:15" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="44"/>
+      <c r="A2" s="46"/>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1604,7 +1607,7 @@
       <c r="K2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="52"/>
+      <c r="L2" s="55"/>
       <c r="M2" s="15"/>
       <c r="N2" s="15"/>
     </row>
@@ -1976,12 +1979,19 @@
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
+      <c r="M10" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="N10">
+        <f>2^N8*(N7-1)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="12" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="53"/>
+      <c r="B12" s="57"/>
       <c r="C12" s="10" t="s">
         <v>3</v>
       </c>
@@ -2005,8 +2015,8 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="54"/>
-      <c r="B13" s="54"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="11">
         <f>C3*$L3</f>
         <v>-16</v>
@@ -2037,8 +2047,8 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="54"/>
-      <c r="B14" s="54"/>
+      <c r="A14" s="59"/>
+      <c r="B14" s="59"/>
       <c r="C14" s="11">
         <f t="shared" ref="C14:I14" si="6">C4*$L4</f>
         <v>22</v>
@@ -2069,8 +2079,8 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="54"/>
-      <c r="B15" s="54"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="11">
         <f t="shared" ref="C15:I15" si="7">C5*$L5</f>
         <v>-20</v>
@@ -2101,8 +2111,8 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="54"/>
-      <c r="B16" s="54"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="59"/>
       <c r="C16" s="11">
         <f t="shared" ref="C16:I16" si="8">C6*$L6</f>
         <v>27</v>
@@ -2133,8 +2143,8 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="54"/>
-      <c r="B17" s="54"/>
+      <c r="A17" s="59"/>
+      <c r="B17" s="59"/>
       <c r="C17" s="11">
         <f t="shared" ref="C17:I17" si="9">C7*$L7</f>
         <v>-21</v>
@@ -2165,8 +2175,8 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="54"/>
-      <c r="B18" s="54"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="11">
         <f t="shared" ref="C18:I18" si="10">C8*$L8</f>
         <v>23</v>
@@ -2197,8 +2207,8 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="54"/>
-      <c r="B19" s="54"/>
+      <c r="A19" s="59"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="11">
         <f t="shared" ref="C19:I19" si="11">C9*$L9</f>
         <v>-18</v>
@@ -2229,8 +2239,8 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="54"/>
-      <c r="B20" s="54"/>
+      <c r="A20" s="59"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="11">
         <f t="shared" ref="C20:I20" si="12">C10*$L10</f>
         <v>30</v>
@@ -2261,8 +2271,8 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="55"/>
-      <c r="B21" s="55"/>
+      <c r="A21" s="60"/>
+      <c r="B21" s="60"/>
       <c r="C21" s="12">
         <f>SUM(C13:C20)</f>
         <v>27</v>
@@ -2296,36 +2306,36 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="53"/>
+      <c r="B22" s="57"/>
       <c r="C22" s="36">
         <f>C21/($N7*2^($N8-1))</f>
         <v>3.375</v>
       </c>
       <c r="D22" s="36">
-        <f t="shared" ref="D22:I22" si="14">D21/($N7*2^($N8-1))</f>
+        <f>D21/($N7*2^($N8-1))</f>
         <v>1.625</v>
       </c>
       <c r="E22" s="6">
-        <f t="shared" si="14"/>
+        <f>E21/($N7*2^($N8-1))</f>
         <v>0.875</v>
       </c>
       <c r="F22" s="36">
-        <f t="shared" si="14"/>
+        <f>F21/($N7*2^($N8-1))</f>
         <v>1.375</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" si="14"/>
+        <f>G21/($N7*2^($N8-1))</f>
         <v>0.125</v>
       </c>
       <c r="H22" s="6">
-        <f t="shared" si="14"/>
+        <f>H21/($N7*2^($N8-1))</f>
         <v>-0.625</v>
       </c>
       <c r="I22" s="6">
-        <f t="shared" si="14"/>
+        <f>I21/($N7*2^($N8-1))</f>
         <v>1.125</v>
       </c>
       <c r="K22" s="22" t="s">
@@ -2333,36 +2343,36 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="53"/>
+      <c r="B23" s="57"/>
       <c r="C23" s="6">
         <f>C21^2/($N7*2^$N8)</f>
         <v>45.5625</v>
       </c>
       <c r="D23" s="6">
-        <f t="shared" ref="D23:I23" si="15">D21^2/($N7*2^$N8)</f>
+        <f>D21^2/($N7*2^$N8)</f>
         <v>10.5625</v>
       </c>
       <c r="E23" s="6">
-        <f t="shared" si="15"/>
+        <f>E21^2/($N7*2^$N8)</f>
         <v>3.0625</v>
       </c>
       <c r="F23" s="6">
-        <f t="shared" si="15"/>
+        <f>F21^2/($N7*2^$N8)</f>
         <v>7.5625</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" si="15"/>
+        <f>G21^2/($N7*2^$N8)</f>
         <v>6.25E-2</v>
       </c>
       <c r="H23" s="6">
-        <f t="shared" si="15"/>
+        <f>H21^2/($N7*2^$N8)</f>
         <v>1.5625</v>
       </c>
       <c r="I23" s="6">
-        <f t="shared" si="15"/>
+        <f>I21^2/($N7*2^$N8)</f>
         <v>5.0625</v>
       </c>
       <c r="K23" s="22" t="s">
@@ -2370,62 +2380,62 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="57" t="s">
+      <c r="A25" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="57"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="50"/>
     </row>
     <row r="26" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="58" t="str">
+      <c r="B26" s="51" t="str">
         <f xml:space="preserve"> N9 &amp; " + " &amp; C22/2 &amp;" x1 + " &amp; D22/2 &amp; " x2 + " &amp; F22/2 &amp; " x1 x2"</f>
         <v>11.0625 + 1.6875 x1 + 0.8125 x2 + 0.6875 x1 x2</v>
       </c>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
     </row>
     <row r="27" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="59" t="s">
+      <c r="A27" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="59"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="59"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
     </row>
     <row r="28" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="56">
+      <c r="B28" s="53">
         <f>11.0625 + 1.6875*(-1)+0.8125*(-1)+0.6875*(-1)*(-1)</f>
         <v>9.25</v>
       </c>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
     </row>
     <row r="30" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C30" s="3" t="s">
@@ -2496,23 +2506,23 @@
         <v>-1</v>
       </c>
       <c r="F32" s="6">
-        <f t="shared" ref="F32:F38" si="16">C32*D32</f>
+        <f t="shared" ref="F32:F38" si="14">C32*D32</f>
         <v>-1</v>
       </c>
       <c r="G32" s="6">
-        <f t="shared" ref="G32:G38" si="17">C32*E32</f>
+        <f t="shared" ref="G32:G38" si="15">C32*E32</f>
         <v>-1</v>
       </c>
       <c r="H32" s="6">
-        <f t="shared" ref="H32:H38" si="18">D32*E32</f>
+        <f t="shared" ref="H32:H38" si="16">D32*E32</f>
         <v>1</v>
       </c>
       <c r="I32" s="6">
-        <f t="shared" ref="I32:I38" si="19">C32*D32*E32</f>
+        <f t="shared" ref="I32:I38" si="17">C32*D32*E32</f>
         <v>1</v>
       </c>
       <c r="J32" s="23">
-        <f t="shared" ref="J32:J38" si="20">$N$9+$C$22/2*C32+$D$22/2*D32+$E$22/2*E32+$F$22/2*F32+$G$22/2*G32+$H$22/2*H32+$I$22/2*I32</f>
+        <f>$N$9+$C$22/2*C32+$D$22/2*D32+$E$22/2*E32+$F$22/2*F32+$G$22/2*G32+$H$22/2*H32+$I$22/2*I32</f>
         <v>11</v>
       </c>
     </row>
@@ -2527,23 +2537,23 @@
         <v>-1</v>
       </c>
       <c r="F33" s="6">
+        <f t="shared" si="14"/>
+        <v>-1</v>
+      </c>
+      <c r="G33" s="6">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="H33" s="6">
         <f t="shared" si="16"/>
         <v>-1</v>
       </c>
-      <c r="G33" s="6">
+      <c r="I33" s="6">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="H33" s="6">
-        <f t="shared" si="18"/>
-        <v>-1</v>
-      </c>
-      <c r="I33" s="6">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
       <c r="J33" s="23">
-        <f t="shared" si="20"/>
+        <f>$N$9+$C$22/2*C33+$D$22/2*D33+$E$22/2*E33+$F$22/2*F33+$G$22/2*G33+$H$22/2*H33+$I$22/2*I33</f>
         <v>10</v>
       </c>
     </row>
@@ -2558,23 +2568,23 @@
         <v>-1</v>
       </c>
       <c r="F34" s="6">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="G34" s="6">
+        <f t="shared" si="15"/>
+        <v>-1</v>
+      </c>
+      <c r="H34" s="6">
         <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="G34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="I34" s="6">
         <f t="shared" si="17"/>
         <v>-1</v>
       </c>
-      <c r="H34" s="6">
-        <f t="shared" si="18"/>
-        <v>-1</v>
-      </c>
-      <c r="I34" s="6">
-        <f t="shared" si="19"/>
-        <v>-1</v>
-      </c>
       <c r="J34" s="23">
-        <f t="shared" si="20"/>
+        <f>$N$9+$C$22/2*C34+$D$22/2*D34+$E$22/2*E34+$F$22/2*F34+$G$22/2*G34+$H$22/2*H34+$I$22/2*I34</f>
         <v>13.5</v>
       </c>
     </row>
@@ -2589,23 +2599,23 @@
         <v>1</v>
       </c>
       <c r="F35" s="6">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="G35" s="6">
+        <f t="shared" si="15"/>
+        <v>-1</v>
+      </c>
+      <c r="H35" s="6">
         <f t="shared" si="16"/>
-        <v>1</v>
-      </c>
-      <c r="G35" s="6">
+        <v>-1</v>
+      </c>
+      <c r="I35" s="6">
         <f t="shared" si="17"/>
-        <v>-1</v>
-      </c>
-      <c r="H35" s="6">
-        <f t="shared" si="18"/>
-        <v>-1</v>
-      </c>
-      <c r="I35" s="6">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="J35" s="23">
-        <f t="shared" si="20"/>
+        <f>$N$9+$C$22/2*C35+$D$22/2*D35+$E$22/2*E35+$F$22/2*F35+$G$22/2*G35+$H$22/2*H35+$I$22/2*I35</f>
         <v>10.5</v>
       </c>
     </row>
@@ -2620,23 +2630,23 @@
         <v>1</v>
       </c>
       <c r="F36" s="6">
+        <f t="shared" si="14"/>
+        <v>-1</v>
+      </c>
+      <c r="G36" s="6">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="H36" s="6">
         <f t="shared" si="16"/>
         <v>-1</v>
       </c>
-      <c r="G36" s="6">
+      <c r="I36" s="6">
         <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="H36" s="6">
-        <f t="shared" si="18"/>
-        <v>-1</v>
-      </c>
-      <c r="I36" s="6">
-        <f t="shared" si="19"/>
         <v>-1</v>
       </c>
       <c r="J36" s="23">
-        <f t="shared" si="20"/>
+        <f>$N$9+$C$22/2*C36+$D$22/2*D36+$E$22/2*E36+$F$22/2*F36+$G$22/2*G36+$H$22/2*H36+$I$22/2*I36</f>
         <v>11.5</v>
       </c>
     </row>
@@ -2651,23 +2661,23 @@
         <v>1</v>
       </c>
       <c r="F37" s="6">
+        <f t="shared" si="14"/>
+        <v>-1</v>
+      </c>
+      <c r="G37" s="6">
+        <f t="shared" si="15"/>
+        <v>-1</v>
+      </c>
+      <c r="H37" s="6">
         <f t="shared" si="16"/>
-        <v>-1</v>
-      </c>
-      <c r="G37" s="6">
+        <v>1</v>
+      </c>
+      <c r="I37" s="6">
         <f t="shared" si="17"/>
         <v>-1</v>
       </c>
-      <c r="H37" s="6">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="I37" s="6">
-        <f t="shared" si="19"/>
-        <v>-1</v>
-      </c>
       <c r="J37" s="23">
-        <f t="shared" si="20"/>
+        <f>$N$9+$C$22/2*C37+$D$22/2*D37+$E$22/2*E37+$F$22/2*F37+$G$22/2*G37+$H$22/2*H37+$I$22/2*I37</f>
         <v>9</v>
       </c>
     </row>
@@ -2682,31 +2692,31 @@
         <v>1</v>
       </c>
       <c r="F38" s="6">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="G38" s="6">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="H38" s="6">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="G38" s="6">
+      <c r="I38" s="6">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="H38" s="6">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="I38" s="6">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
       <c r="J38" s="23">
-        <f t="shared" si="20"/>
+        <f>$N$9+$C$22/2*C38+$D$22/2*D38+$E$22/2*E38+$F$22/2*F38+$G$22/2*G38+$H$22/2*H38+$I$22/2*I38</f>
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="3:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J39" s="51" t="s">
+      <c r="J39" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="K39" s="52"/>
+      <c r="K39" s="55"/>
     </row>
     <row r="40" spans="3:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J40" s="16" t="s">
@@ -2718,31 +2728,31 @@
     </row>
     <row r="41" spans="3:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J41" s="18">
-        <f t="shared" ref="J41:K41" si="21">J3-$J31</f>
+        <f t="shared" ref="J41:K41" si="18">J3-$J31</f>
         <v>1</v>
       </c>
       <c r="K41" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="18"/>
         <v>-1</v>
       </c>
     </row>
     <row r="42" spans="3:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J42" s="18">
-        <f t="shared" ref="J42:K42" si="22">J4-$J32</f>
+        <f t="shared" ref="J42:K42" si="19">J4-$J32</f>
         <v>-1</v>
       </c>
       <c r="K42" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="3:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J43" s="18">
-        <f t="shared" ref="J43:K43" si="23">J5-$J33</f>
+        <f t="shared" ref="J43:K43" si="20">J5-$J33</f>
         <v>-1</v>
       </c>
       <c r="K43" s="18">
-        <f t="shared" si="23"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
     </row>
@@ -2758,31 +2768,31 @@
     </row>
     <row r="45" spans="3:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J45" s="18">
-        <f t="shared" ref="J45:K45" si="24">J7-$J35</f>
+        <f t="shared" ref="J45:K45" si="21">J7-$J35</f>
         <v>0.5</v>
       </c>
       <c r="K45" s="18">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>-0.5</v>
       </c>
     </row>
     <row r="46" spans="3:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J46" s="18">
-        <f t="shared" ref="J46:K46" si="25">J8-$J36</f>
+        <f t="shared" ref="J46:K46" si="22">J8-$J36</f>
         <v>-1.5</v>
       </c>
       <c r="K46" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>1.5</v>
       </c>
     </row>
     <row r="47" spans="3:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J47" s="18">
-        <f t="shared" ref="J47:K47" si="26">J9-$J37</f>
+        <f t="shared" ref="J47:K47" si="23">J9-$J37</f>
         <v>1</v>
       </c>
       <c r="K47" s="18">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>-1</v>
       </c>
       <c r="L47" s="16" t="s">
@@ -2812,14 +2822,14 @@
       </c>
     </row>
     <row r="50" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="60" t="s">
+      <c r="A50" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="B50" s="57"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="57"/>
-      <c r="F50" s="57"/>
+      <c r="B50" s="50"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="50"/>
       <c r="G50"/>
       <c r="H50"/>
       <c r="I50"/>
@@ -2897,15 +2907,15 @@
         <v>1</v>
       </c>
       <c r="D53" s="7">
-        <f t="shared" ref="D53:D58" si="27">B53/C53</f>
+        <f t="shared" ref="D53:D58" si="24">B53/C53</f>
         <v>10.5625</v>
       </c>
       <c r="E53" s="7">
-        <f t="shared" ref="E53:E58" si="28">D53/$D$59</f>
+        <f t="shared" ref="E53:E58" si="25">D53/$D$59</f>
         <v>4.333333333333333</v>
       </c>
       <c r="F53" s="7">
-        <f t="shared" ref="F53:F58" si="29">_xlfn.F.DIST.RT(E53, C53, $C$59)</f>
+        <f t="shared" ref="F53:F58" si="26">_xlfn.F.DIST.RT(E53, C53, $C$59)</f>
         <v>7.0931245153521144E-2</v>
       </c>
       <c r="G53" s="26" t="s">
@@ -2924,15 +2934,15 @@
         <v>1</v>
       </c>
       <c r="D54" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>3.0625</v>
       </c>
       <c r="E54" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>1.2564102564102564</v>
       </c>
       <c r="F54" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>0.29484895930913857</v>
       </c>
       <c r="G54" s="26"/>
@@ -2949,15 +2959,15 @@
         <v>1</v>
       </c>
       <c r="D55" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>7.5625</v>
       </c>
       <c r="E55" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>3.1025641025641026</v>
       </c>
       <c r="F55" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>0.11619707388209986</v>
       </c>
       <c r="G55" s="26"/>
@@ -2974,15 +2984,15 @@
         <v>1</v>
       </c>
       <c r="D56" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>6.25E-2</v>
       </c>
       <c r="E56" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2.564102564102564E-2</v>
       </c>
       <c r="F56" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>0.87674946427651212</v>
       </c>
       <c r="G56" s="26"/>
@@ -2999,15 +3009,15 @@
         <v>1</v>
       </c>
       <c r="D57" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>1.5625</v>
       </c>
       <c r="E57" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>0.64102564102564108</v>
       </c>
       <c r="F57" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>0.4464629199074549</v>
       </c>
       <c r="G57" s="26"/>
@@ -3024,15 +3034,15 @@
         <v>1</v>
       </c>
       <c r="D58" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="24"/>
         <v>5.0625</v>
       </c>
       <c r="E58" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="25"/>
         <v>2.0769230769230771</v>
       </c>
       <c r="F58" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="26"/>
         <v>0.18751226181309197</v>
       </c>
       <c r="G58" s="26"/>
@@ -3073,85 +3083,85 @@
       </c>
     </row>
     <row r="64" spans="1:14" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="57" t="s">
+      <c r="A64" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="B64" s="57"/>
-      <c r="C64" s="57"/>
-      <c r="D64" s="57"/>
-      <c r="E64" s="57"/>
-      <c r="F64" s="57"/>
-      <c r="G64" s="57"/>
-      <c r="H64" s="57"/>
-      <c r="I64" s="57"/>
+      <c r="B64" s="50"/>
+      <c r="C64" s="50"/>
+      <c r="D64" s="50"/>
+      <c r="E64" s="50"/>
+      <c r="F64" s="50"/>
+      <c r="G64" s="50"/>
+      <c r="H64" s="50"/>
+      <c r="I64" s="50"/>
     </row>
     <row r="65" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B65" s="58" t="str">
+      <c r="B65" s="51" t="str">
         <f xml:space="preserve"> N9 &amp; " + " &amp; C22/2 &amp;" x1 + " &amp; D22/2 &amp; " x2 + " &amp; F22/2 &amp; " x1 x2"</f>
         <v>11.0625 + 1.6875 x1 + 0.8125 x2 + 0.6875 x1 x2</v>
       </c>
-      <c r="C65" s="58"/>
-      <c r="D65" s="58"/>
-      <c r="E65" s="58"/>
-      <c r="F65" s="58"/>
-      <c r="G65" s="58"/>
-      <c r="H65" s="58"/>
-      <c r="I65" s="58"/>
+      <c r="C65" s="51"/>
+      <c r="D65" s="51"/>
+      <c r="E65" s="51"/>
+      <c r="F65" s="51"/>
+      <c r="G65" s="51"/>
+      <c r="H65" s="51"/>
+      <c r="I65" s="51"/>
     </row>
     <row r="66" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="59" t="s">
+      <c r="A66" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B66" s="59"/>
-      <c r="C66" s="59"/>
-      <c r="D66" s="59"/>
-      <c r="E66" s="59"/>
-      <c r="F66" s="59"/>
-      <c r="G66" s="59"/>
-      <c r="H66" s="59"/>
-      <c r="I66" s="59"/>
+      <c r="B66" s="52"/>
+      <c r="C66" s="52"/>
+      <c r="D66" s="52"/>
+      <c r="E66" s="52"/>
+      <c r="F66" s="52"/>
+      <c r="G66" s="52"/>
+      <c r="H66" s="52"/>
+      <c r="I66" s="52"/>
     </row>
     <row r="67" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B67" s="56">
+      <c r="B67" s="53">
         <f>11.0625 + 1.6875*(-1)+0.8125*(-1)</f>
         <v>8.5625</v>
       </c>
-      <c r="C67" s="56"/>
-      <c r="D67" s="56"/>
-      <c r="E67" s="56"/>
-      <c r="F67" s="56"/>
-      <c r="G67" s="56"/>
-      <c r="H67" s="56"/>
-      <c r="I67" s="56"/>
+      <c r="C67" s="53"/>
+      <c r="D67" s="53"/>
+      <c r="E67" s="53"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="53"/>
+      <c r="H67" s="53"/>
+      <c r="I67" s="53"/>
       <c r="J67" t="s">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="A12:B21"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A64:I64"/>
     <mergeCell ref="B65:I65"/>
     <mergeCell ref="A66:I66"/>
     <mergeCell ref="B67:I67"/>
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="A50:F50"/>
-    <mergeCell ref="B28:I28"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="A12:B21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3190,33 +3200,33 @@
       </c>
     </row>
     <row r="6" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="46" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
+      <c r="C6" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="46"/>
+      <c r="Q6" s="46"/>
+      <c r="R6" s="46"/>
     </row>
     <row r="7" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="44"/>
+      <c r="A7" s="46"/>
       <c r="B7" s="64"/>
       <c r="C7" s="3" t="s">
         <v>2</v>
@@ -5664,17 +5674,17 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="57" t="s">
+      <c r="A46" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="B46" s="57"/>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="57"/>
+      <c r="B46" s="50"/>
+      <c r="C46" s="50"/>
+      <c r="D46" s="50"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="50"/>
+      <c r="G46" s="50"/>
+      <c r="H46" s="50"/>
+      <c r="I46" s="50"/>
     </row>
     <row r="47" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="14" t="s">
@@ -5683,29 +5693,29 @@
       <c r="B47" s="61" t="s">
         <v>83</v>
       </c>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="58"/>
+      <c r="C47" s="51"/>
+      <c r="D47" s="51"/>
+      <c r="E47" s="51"/>
+      <c r="F47" s="51"/>
+      <c r="G47" s="51"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="51"/>
       <c r="J47" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="59" t="s">
+      <c r="A48" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="B48" s="59"/>
-      <c r="C48" s="59"/>
-      <c r="D48" s="59"/>
-      <c r="E48" s="59"/>
-      <c r="F48" s="59"/>
-      <c r="G48" s="59"/>
-      <c r="H48" s="59"/>
-      <c r="I48" s="59"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="52"/>
     </row>
     <row r="49" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="14" t="s">
@@ -5715,13 +5725,13 @@
         <f xml:space="preserve"> (D43/2 * (-1) ) + (G43/2 * (-1)) + (J43/2 * (-1)*(-1)) + AVERAGE(B8:B23)</f>
         <v>597</v>
       </c>
-      <c r="C49" s="56"/>
-      <c r="D49" s="56"/>
-      <c r="E49" s="56"/>
-      <c r="F49" s="56"/>
-      <c r="G49" s="56"/>
-      <c r="H49" s="56"/>
-      <c r="I49" s="56"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -5771,30 +5781,30 @@
       </c>
     </row>
     <row r="6" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
+      <c r="B6" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="46"/>
+      <c r="Q6" s="46"/>
     </row>
     <row r="7" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="44"/>
+      <c r="A7" s="46"/>
       <c r="B7" s="3" t="s">
         <v>2</v>
       </c>
@@ -6884,10 +6894,10 @@
       <c r="E25" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="45" t="s">
+      <c r="F25" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="G25" s="46"/>
+      <c r="G25" s="48"/>
       <c r="H25" s="3" t="s">
         <v>64</v>
       </c>
@@ -6921,10 +6931,10 @@
         <f>B26*C26*D26</f>
         <v>-1</v>
       </c>
-      <c r="F26" s="47" t="s">
+      <c r="F26" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="G26" s="43"/>
+      <c r="G26" s="45"/>
       <c r="H26" s="5">
         <v>550</v>
       </c>
@@ -6963,10 +6973,10 @@
         <f t="shared" ref="E27:E33" si="14">B27*C27*D27</f>
         <v>1</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="G27" s="43"/>
+      <c r="G27" s="45"/>
       <c r="H27" s="5">
         <v>749</v>
       </c>
@@ -7005,10 +7015,10 @@
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="F28" s="42" t="s">
+      <c r="F28" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="G28" s="43"/>
+      <c r="G28" s="45"/>
       <c r="H28" s="5">
         <v>1052</v>
       </c>
@@ -7047,10 +7057,10 @@
         <f t="shared" si="14"/>
         <v>-1</v>
       </c>
-      <c r="F29" s="42" t="s">
+      <c r="F29" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="G29" s="43"/>
+      <c r="G29" s="45"/>
       <c r="H29" s="5">
         <v>650</v>
       </c>
@@ -7089,10 +7099,10 @@
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="F30" s="42" t="s">
+      <c r="F30" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="G30" s="43"/>
+      <c r="G30" s="45"/>
       <c r="H30" s="5">
         <v>1075</v>
       </c>
@@ -7131,10 +7141,10 @@
         <f t="shared" si="14"/>
         <v>-1</v>
       </c>
-      <c r="F31" s="42" t="s">
+      <c r="F31" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="43"/>
+      <c r="G31" s="45"/>
       <c r="H31" s="5">
         <v>642</v>
       </c>
@@ -7173,10 +7183,10 @@
         <f t="shared" si="14"/>
         <v>-1</v>
       </c>
-      <c r="F32" s="42" t="s">
+      <c r="F32" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="G32" s="43"/>
+      <c r="G32" s="45"/>
       <c r="H32" s="5">
         <v>601</v>
       </c>
@@ -7215,10 +7225,10 @@
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="F33" s="42" t="s">
+      <c r="F33" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="G33" s="43"/>
+      <c r="G33" s="45"/>
       <c r="H33" s="5">
         <v>729</v>
       </c>
@@ -7247,7 +7257,7 @@
       <c r="K34" s="5"/>
     </row>
     <row r="35" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="48" t="s">
+      <c r="A35" s="42" t="s">
         <v>22</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -7283,7 +7293,7 @@
       </c>
     </row>
     <row r="36" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="48"/>
+      <c r="A36" s="42"/>
       <c r="B36" s="5">
         <f>B26*$H26</f>
         <v>-550</v>
@@ -7323,7 +7333,7 @@
       </c>
     </row>
     <row r="37" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="48"/>
+      <c r="A37" s="42"/>
       <c r="B37" s="5">
         <f t="shared" ref="B37:E37" si="22">B27*$H27</f>
         <v>749</v>
@@ -7362,7 +7372,7 @@
       </c>
     </row>
     <row r="38" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="48"/>
+      <c r="A38" s="42"/>
       <c r="B38" s="5">
         <f t="shared" ref="B38:E38" si="24">B28*$H28</f>
         <v>-1052</v>
@@ -7401,7 +7411,7 @@
       </c>
     </row>
     <row r="39" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="48"/>
+      <c r="A39" s="42"/>
       <c r="B39" s="5">
         <f t="shared" ref="B39:E39" si="26">B29*$H29</f>
         <v>650</v>
@@ -7440,7 +7450,7 @@
       </c>
     </row>
     <row r="40" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="48"/>
+      <c r="A40" s="42"/>
       <c r="B40" s="5">
         <f t="shared" ref="B40:E40" si="28">B30*$H30</f>
         <v>-1075</v>
@@ -7479,7 +7489,7 @@
       </c>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="48"/>
+      <c r="A41" s="42"/>
       <c r="B41" s="5">
         <f t="shared" ref="B41:E41" si="30">B31*$H31</f>
         <v>642</v>
@@ -7518,7 +7528,7 @@
       </c>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="48"/>
+      <c r="A42" s="42"/>
       <c r="B42" s="5">
         <f t="shared" ref="B42:E42" si="32">B32*$H32</f>
         <v>-601</v>
@@ -7560,7 +7570,7 @@
       </c>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="48"/>
+      <c r="A43" s="42"/>
       <c r="B43" s="5">
         <f t="shared" ref="B43:E43" si="33">B33*$H33</f>
         <v>729</v>
@@ -7608,7 +7618,7 @@
       </c>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="49"/>
+      <c r="A44" s="43"/>
       <c r="B44" s="5">
         <f>SUM(B36:B43)</f>
         <v>-508</v>
@@ -7740,18 +7750,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:Q6"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
     <mergeCell ref="A35:A44"/>
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:Q6"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
